--- a/graphy/감사조서/graphy_mapping_list_26년2Q.xlsx
+++ b/graphy/감사조서/graphy_mapping_list_26년2Q.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD947C2F-9BEF-444E-99C3-AE395B9CF468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD9913-77B7-4EB1-8B93-D208ACF7B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="157">
   <si>
     <t>계정명</t>
   </si>
@@ -1292,6 +1292,242 @@
     <t>보통예금</t>
   </si>
   <si>
+    <t>JET_25년</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보통예금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차변</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보통예금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변</t>
+    </r>
+  </si>
+  <si>
+    <t>미지급금</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벤포드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미지급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대변</t>
+    </r>
+  </si>
+  <si>
+    <t>공휴일전표</t>
+  </si>
+  <si>
     <r>
       <t>graphy_</t>
     </r>
@@ -1303,411 +1539,6 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>차변</t>
-    </r>
-  </si>
-  <si>
-    <t>JET_25년</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>차변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보통예금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변</t>
-    </r>
-  </si>
-  <si>
-    <t>미지급금</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>미지급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벤포드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>미지급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대변</t>
-    </r>
-  </si>
-  <si>
-    <t>공휴일전표</t>
-  </si>
-  <si>
-    <r>
-      <t>graphy_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
       <t>공휴일전표</t>
     </r>
   </si>
@@ -1757,25 +1588,16 @@
     <t>보통예금_차변_그래프</t>
   </si>
   <si>
-    <t>graphy_벤포드_보통예금_차변</t>
-  </si>
-  <si>
     <t>벤포드 분석_보통예금_차변</t>
   </si>
   <si>
     <t>보통예금_대변_그래프</t>
   </si>
   <si>
-    <t>graphy_벤포드_보통예금_대변</t>
-  </si>
-  <si>
     <t>벤포드 분석_보통예금_대변</t>
   </si>
   <si>
     <t>미지급금_그래프</t>
-  </si>
-  <si>
-    <t>graphy_벤포드_미지급금_대변</t>
   </si>
   <si>
     <t>벤포드 분석_미지급금_대변</t>
@@ -2024,6 +1846,95 @@
       <t>해외상품매출액</t>
     </r>
     <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>graphy_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벤포드법칙분석</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>외상매출금_차변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>외상매입금_대변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>국내상품매출액_대변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>해외상품매출액_대변</t>
+  </si>
+  <si>
+    <t>해외상품매출액_대변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국내제품매출액</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대변</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>해외제품매출액_대변</t>
+  </si>
+  <si>
+    <t>해외제품매출액_대변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금_차변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금_대변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>미지급금_대변</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>국내제품매출액_대변</t>
   </si>
 </sst>
 </file>
@@ -2571,7 +2482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.25" style="1" customWidth="1"/>
@@ -2793,7 +2704,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>11</v>
@@ -2818,7 +2729,7 @@
         <v>41</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>11</v>
@@ -3148,7 +3059,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>69</v>
@@ -3207,7 +3118,7 @@
         <v>83</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="10"/>
@@ -3230,7 +3141,7 @@
         <v>85</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="10"/>
@@ -3253,7 +3164,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="10"/>
@@ -3276,7 +3187,7 @@
         <v>89</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="10"/>
@@ -3338,17 +3249,17 @@
         <v>99</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>56</v>
@@ -3361,17 +3272,17 @@
         <v>99</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>56</v>
@@ -3384,14 +3295,14 @@
         <v>9</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>55</v>
@@ -3407,14 +3318,14 @@
         <v>22</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>58</v>
@@ -3427,20 +3338,20 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>56</v>
@@ -3453,14 +3364,14 @@
         <v>59</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>61</v>
@@ -3476,14 +3387,14 @@
         <v>26</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>63</v>
@@ -3499,14 +3410,14 @@
         <v>30</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>65</v>
@@ -3522,14 +3433,14 @@
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>67</v>
@@ -3542,209 +3453,223 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>69</v>
+        <v>144</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="8" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H41" s="7"/>
-      <c r="I41" s="10"/>
+      <c r="I41" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>69</v>
+        <v>144</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="8" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H42" s="7"/>
-      <c r="I42" s="10"/>
+      <c r="I42" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>69</v>
+        <v>144</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>74</v>
+        <v>13</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H43" s="7"/>
-      <c r="I43" s="10"/>
+      <c r="I43" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>76</v>
+        <v>13</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H44" s="7"/>
-      <c r="I44" s="10"/>
+      <c r="I44" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>69</v>
+        <v>144</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="8" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H45" s="7"/>
-      <c r="I45" s="10"/>
+      <c r="I45" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="8" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H46" s="7"/>
-      <c r="I46" s="10"/>
+      <c r="I46" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="H47" s="7"/>
-      <c r="I47" s="10"/>
+      <c r="I47" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D48" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" s="7"/>
+      <c r="E48" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="8" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="10" t="s">
@@ -3753,403 +3678,239 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="4" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="8" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="H50" s="7"/>
-      <c r="I50" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I50" s="10"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="4" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="8" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="H51" s="7"/>
-      <c r="I51" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I51" s="10"/>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="4" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>119</v>
+        <v>100</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="H52" s="7"/>
-      <c r="I52" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I52" s="10"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="4" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>121</v>
+        <v>100</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="H53" s="7"/>
-      <c r="I53" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I53" s="10"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="4" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="8" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="H54" s="7"/>
-      <c r="I54" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I54" s="10"/>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="4" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="H55" s="7"/>
-      <c r="I55" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I55" s="10"/>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="4" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H56" s="7"/>
-      <c r="I56" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="I56" s="10"/>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" s="7"/>
+        <v>92</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>108</v>
+      </c>
       <c r="E57" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>55</v>
+        <v>100</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>131</v>
+      </c>
+      <c r="H57" s="13"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" ht="17" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" s="7"/>
+        <v>134</v>
+      </c>
+      <c r="D58" s="15"/>
       <c r="E58" s="8" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>136</v>
+      </c>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+    </row>
+    <row r="59" spans="1:9" ht="17" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" s="7"/>
+        <v>140</v>
+      </c>
+      <c r="D59" s="15"/>
       <c r="E59" s="8" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D62" s="7"/>
-      <c r="E62" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D63" s="7"/>
-      <c r="E63" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H63" s="7"/>
-      <c r="I63" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="17" customHeight="1">
-      <c r="A64" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+    </row>
+    <row r="65" spans="2:2" ht="17" customHeight="1">
+      <c r="B65" s="14" t="s">
         <v>138</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D64" s="15"/>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-    </row>
-    <row r="65" spans="1:9" ht="17" customHeight="1">
-      <c r="A65" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D65" s="15"/>
-      <c r="E65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-    </row>
-    <row r="71" spans="1:9" ht="17" customHeight="1">
-      <c r="B71" s="14" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
